--- a/Flujo de Efectivo/Datos flujo de efectivo.xlsx
+++ b/Flujo de Efectivo/Datos flujo de efectivo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivannaherrera/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luill\OneDrive\Documentos\Clases ITESO\PAP\V2026\Flujo de Efectivo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11E00AF-75CF-4A4E-9155-D5735A1A2395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CE5367-8741-44BA-944B-6680F800BB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{946F2282-48A8-C141-8164-58702EF69A48}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{946F2282-48A8-C141-8164-58702EF69A48}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="243">
   <si>
     <t>18-23 mayo</t>
   </si>
@@ -708,6 +708,66 @@
   </si>
   <si>
     <t>Gasto regreso</t>
+  </si>
+  <si>
+    <t>Proveedores Fruta</t>
+  </si>
+  <si>
+    <t>Insumos</t>
+  </si>
+  <si>
+    <t>Mantenimiento</t>
+  </si>
+  <si>
+    <t>Caja</t>
+  </si>
+  <si>
+    <t>Etiqueta</t>
+  </si>
+  <si>
+    <t>Bolsa</t>
+  </si>
+  <si>
+    <t>Tarima</t>
+  </si>
+  <si>
+    <t>Laboratorio</t>
+  </si>
+  <si>
+    <t>Intereses</t>
+  </si>
+  <si>
+    <t>Seguros</t>
+  </si>
+  <si>
+    <t>Gastos CXM</t>
+  </si>
+  <si>
+    <t>Gastos AVV</t>
+  </si>
+  <si>
+    <t>Contador</t>
+  </si>
+  <si>
+    <t>Emplaye</t>
+  </si>
+  <si>
+    <t>Certificación</t>
+  </si>
+  <si>
+    <t>Préstamo</t>
+  </si>
+  <si>
+    <t>Nómina Proberry</t>
+  </si>
+  <si>
+    <t>Transporte</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>Maquinaria</t>
   </si>
 </sst>
 </file>
@@ -737,6 +797,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -836,7 +897,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
+      <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1206,19 +1267,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C19CF6CA-3BFF-934C-8943-6DE16D6E27F2}">
   <dimension ref="A1:F537"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.296875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.796875" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.5" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="1"/>
+    <col min="7" max="7" width="10.796875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>37</v>
       </c>
@@ -1238,7 +1299,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>46167</v>
       </c>
@@ -1258,7 +1319,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>46167</v>
       </c>
@@ -1278,7 +1339,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>46167</v>
       </c>
@@ -1298,7 +1359,7 @@
         <v>13091.400000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>46167</v>
       </c>
@@ -1309,7 +1370,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>4</v>
@@ -1318,7 +1379,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>46167</v>
       </c>
@@ -1329,7 +1390,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>227</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>5</v>
@@ -1338,7 +1399,7 @@
         <v>4172.1099999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>46167</v>
       </c>
@@ -1349,7 +1410,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>6</v>
@@ -1358,7 +1419,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>46167</v>
       </c>
@@ -1369,7 +1430,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>7</v>
@@ -1378,7 +1439,7 @@
         <v>3596</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>46167</v>
       </c>
@@ -1398,7 +1459,7 @@
         <v>26453.739999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>46167</v>
       </c>
@@ -1409,7 +1470,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>32</v>
+        <v>229</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>9</v>
@@ -1418,7 +1479,7 @@
         <v>15370</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>46167</v>
       </c>
@@ -1429,7 +1490,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>10</v>
@@ -1438,7 +1499,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>46167</v>
       </c>
@@ -1449,7 +1510,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>10</v>
@@ -1458,7 +1519,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>46167</v>
       </c>
@@ -1469,7 +1530,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>11</v>
@@ -1478,7 +1539,7 @@
         <v>31215.599999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>46167</v>
       </c>
@@ -1489,7 +1550,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>11</v>
@@ -1498,7 +1559,7 @@
         <v>9802</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>46167</v>
       </c>
@@ -1509,7 +1570,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>11</v>
@@ -1518,7 +1579,7 @@
         <v>13722.799999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>46167</v>
       </c>
@@ -1529,7 +1590,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>32</v>
+        <v>230</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>12</v>
@@ -1538,7 +1599,7 @@
         <v>6086.26</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>46167</v>
       </c>
@@ -1549,7 +1610,7 @@
         <v>15</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>231</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>13</v>
@@ -1558,7 +1619,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>46167</v>
       </c>
@@ -1578,7 +1639,7 @@
         <v>13428</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>46167</v>
       </c>
@@ -1589,7 +1650,7 @@
         <v>15</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>28</v>
@@ -1598,7 +1659,7 @@
         <v>4750</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>46167</v>
       </c>
@@ -1609,7 +1670,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>21</v>
@@ -1618,7 +1679,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>46167</v>
       </c>
@@ -1629,7 +1690,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>22</v>
@@ -1638,7 +1699,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>46167</v>
       </c>
@@ -1649,7 +1710,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>23</v>
@@ -1658,7 +1719,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>46167</v>
       </c>
@@ -1669,7 +1730,7 @@
         <v>15</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>24</v>
@@ -1678,7 +1739,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>46167</v>
       </c>
@@ -1698,7 +1759,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>46167</v>
       </c>
@@ -1718,7 +1779,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>46167</v>
       </c>
@@ -1729,7 +1790,7 @@
         <v>15</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>27</v>
@@ -1738,7 +1799,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>46167</v>
       </c>
@@ -1758,7 +1819,7 @@
         <v>184700</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>46167</v>
       </c>
@@ -1778,7 +1839,7 @@
         <v>127000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>46160</v>
       </c>
@@ -1798,7 +1859,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>46160</v>
       </c>
@@ -1818,7 +1879,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>46160</v>
       </c>
@@ -1838,7 +1899,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>46160</v>
       </c>
@@ -1858,7 +1919,7 @@
         <v>8670.8160000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>46160</v>
       </c>
@@ -1869,7 +1930,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>32</v>
+        <v>229</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>39</v>
@@ -1878,7 +1939,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>46160</v>
       </c>
@@ -1889,7 +1950,7 @@
         <v>15</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>40</v>
@@ -1898,7 +1959,7 @@
         <v>7134</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>46160</v>
       </c>
@@ -1909,7 +1970,7 @@
         <v>15</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>7</v>
@@ -1918,7 +1979,7 @@
         <v>3596</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>46160</v>
       </c>
@@ -1929,7 +1990,7 @@
         <v>15</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>41</v>
@@ -1938,7 +1999,7 @@
         <v>2729</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>46160</v>
       </c>
@@ -1949,7 +2010,7 @@
         <v>15</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>11</v>
@@ -1958,7 +2019,7 @@
         <v>14697.2</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>46160</v>
       </c>
@@ -1978,7 +2039,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>46160</v>
       </c>
@@ -1989,7 +2050,7 @@
         <v>15</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>28</v>
@@ -1998,7 +2059,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>46160</v>
       </c>
@@ -2009,7 +2070,7 @@
         <v>15</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>21</v>
@@ -2018,7 +2079,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>46160</v>
       </c>
@@ -2029,7 +2090,7 @@
         <v>15</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>22</v>
@@ -2038,7 +2099,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>46160</v>
       </c>
@@ -2049,7 +2110,7 @@
         <v>15</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>35</v>
+        <v>233</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>43</v>
@@ -2058,7 +2119,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>46160</v>
       </c>
@@ -2069,7 +2130,7 @@
         <v>15</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>23</v>
@@ -2078,7 +2139,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>46160</v>
       </c>
@@ -2089,7 +2150,7 @@
         <v>15</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>24</v>
@@ -2098,7 +2159,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>46160</v>
       </c>
@@ -2109,7 +2170,7 @@
         <v>15</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>27</v>
@@ -2118,7 +2179,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>46160</v>
       </c>
@@ -2138,7 +2199,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>46160</v>
       </c>
@@ -2158,7 +2219,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>46160</v>
       </c>
@@ -2178,7 +2239,7 @@
         <v>206448</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>46153</v>
       </c>
@@ -2198,7 +2259,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>46153</v>
       </c>
@@ -2218,7 +2279,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>46153</v>
       </c>
@@ -2238,7 +2299,7 @@
         <v>24450</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>46153</v>
       </c>
@@ -2258,7 +2319,7 @@
         <v>13795.488000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>46153</v>
       </c>
@@ -2269,7 +2330,7 @@
         <v>15</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>47</v>
@@ -2278,7 +2339,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>46153</v>
       </c>
@@ -2289,7 +2350,7 @@
         <v>15</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>47</v>
@@ -2298,7 +2359,7 @@
         <v>61302.86</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>46153</v>
       </c>
@@ -2309,7 +2370,7 @@
         <v>15</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>4</v>
@@ -2318,7 +2379,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>46153</v>
       </c>
@@ -2329,7 +2390,7 @@
         <v>15</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>48</v>
@@ -2338,7 +2399,7 @@
         <v>8952.2999999999993</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>46153</v>
       </c>
@@ -2349,7 +2410,7 @@
         <v>15</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>49</v>
@@ -2358,7 +2419,7 @@
         <v>6666.98</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>46153</v>
       </c>
@@ -2369,7 +2430,7 @@
         <v>15</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>19</v>
+        <v>225</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>50</v>
@@ -2378,7 +2439,7 @@
         <v>7508.23</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>46153</v>
       </c>
@@ -2398,7 +2459,7 @@
         <v>14685.06</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>46153</v>
       </c>
@@ -2409,7 +2470,7 @@
         <v>15</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>52</v>
@@ -2418,7 +2479,7 @@
         <v>9800</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>46153</v>
       </c>
@@ -2429,7 +2490,7 @@
         <v>15</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>11</v>
@@ -2438,7 +2499,7 @@
         <v>56045.4</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>46153</v>
       </c>
@@ -2449,7 +2510,7 @@
         <v>15</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>11</v>
@@ -2458,7 +2519,7 @@
         <v>9802</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>46153</v>
       </c>
@@ -2469,7 +2530,7 @@
         <v>15</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>32</v>
+        <v>224</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>53</v>
@@ -2478,7 +2539,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>46153</v>
       </c>
@@ -2489,7 +2550,7 @@
         <v>15</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>32</v>
+        <v>224</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>54</v>
@@ -2498,7 +2559,7 @@
         <v>4674</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>46153</v>
       </c>
@@ -2518,7 +2579,7 @@
         <v>10801</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>46153</v>
       </c>
@@ -2529,7 +2590,7 @@
         <v>15</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>28</v>
@@ -2538,7 +2599,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>46153</v>
       </c>
@@ -2549,7 +2610,7 @@
         <v>15</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>21</v>
@@ -2558,7 +2619,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>46153</v>
       </c>
@@ -2569,7 +2630,7 @@
         <v>15</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>22</v>
@@ -2578,7 +2639,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>46153</v>
       </c>
@@ -2589,7 +2650,7 @@
         <v>15</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>23</v>
@@ -2598,7 +2659,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>46153</v>
       </c>
@@ -2609,7 +2670,7 @@
         <v>15</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>35</v>
+        <v>233</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>56</v>
@@ -2618,7 +2679,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>46153</v>
       </c>
@@ -2629,7 +2690,7 @@
         <v>15</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>24</v>
@@ -2638,7 +2699,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>46153</v>
       </c>
@@ -2649,7 +2710,7 @@
         <v>15</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>57</v>
@@ -2658,7 +2719,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>46153</v>
       </c>
@@ -2669,7 +2730,7 @@
         <v>15</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>58</v>
@@ -2678,7 +2739,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>46153</v>
       </c>
@@ -2698,7 +2759,7 @@
         <v>199760</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>46153</v>
       </c>
@@ -2718,7 +2779,7 @@
         <v>128704</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>46153</v>
       </c>
@@ -2738,7 +2799,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>46146</v>
       </c>
@@ -2758,7 +2819,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>46146</v>
       </c>
@@ -2778,7 +2839,7 @@
         <v>21850</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>46146</v>
       </c>
@@ -2798,7 +2859,7 @@
         <v>5537.7000000000007</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>46146</v>
       </c>
@@ -2809,7 +2870,7 @@
         <v>15</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>32</v>
+        <v>236</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>63</v>
@@ -2818,7 +2879,7 @@
         <v>4235.9399999999996</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>46146</v>
       </c>
@@ -2829,7 +2890,7 @@
         <v>15</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>32</v>
+        <v>229</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>9</v>
@@ -2838,7 +2899,7 @@
         <v>15370</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>46146</v>
       </c>
@@ -2849,7 +2910,7 @@
         <v>15</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>11</v>
@@ -2858,7 +2919,7 @@
         <v>18270</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>46146</v>
       </c>
@@ -2869,7 +2930,7 @@
         <v>15</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>32</v>
+        <v>224</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>53</v>
@@ -2878,7 +2939,7 @@
         <v>4750.2</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>46146</v>
       </c>
@@ -2889,7 +2950,7 @@
         <v>15</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>28</v>
@@ -2898,7 +2959,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>46146</v>
       </c>
@@ -2909,7 +2970,7 @@
         <v>15</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>21</v>
@@ -2918,7 +2979,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>46146</v>
       </c>
@@ -2929,7 +2990,7 @@
         <v>15</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>22</v>
@@ -2938,7 +2999,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>46146</v>
       </c>
@@ -2949,7 +3010,7 @@
         <v>15</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>23</v>
@@ -2958,7 +3019,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>46146</v>
       </c>
@@ -2969,7 +3030,7 @@
         <v>15</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>64</v>
@@ -2978,7 +3039,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>46146</v>
       </c>
@@ -2989,7 +3050,7 @@
         <v>15</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>24</v>
@@ -2998,7 +3059,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>46146</v>
       </c>
@@ -3009,7 +3070,7 @@
         <v>15</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>27</v>
@@ -3018,7 +3079,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>46146</v>
       </c>
@@ -3029,7 +3090,7 @@
         <v>15</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>57</v>
@@ -3038,7 +3099,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>46146</v>
       </c>
@@ -3058,7 +3119,7 @@
         <v>193267.8</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>46139</v>
       </c>
@@ -3078,7 +3139,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>46139</v>
       </c>
@@ -3098,7 +3159,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>46139</v>
       </c>
@@ -3118,7 +3179,7 @@
         <v>15645</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>46139</v>
       </c>
@@ -3138,7 +3199,7 @@
         <v>19750</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>46139</v>
       </c>
@@ -3158,7 +3219,7 @@
         <v>6526.59</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>46139</v>
       </c>
@@ -3169,7 +3230,7 @@
         <v>15</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>67</v>
@@ -3178,7 +3239,7 @@
         <v>10788</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>46139</v>
       </c>
@@ -3189,7 +3250,7 @@
         <v>15</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>49</v>
@@ -3198,7 +3259,7 @@
         <v>7222</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>46139</v>
       </c>
@@ -3209,7 +3270,7 @@
         <v>15</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>4</v>
@@ -3218,7 +3279,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>46139</v>
       </c>
@@ -3229,7 +3290,7 @@
         <v>15</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>68</v>
@@ -3238,7 +3299,7 @@
         <v>2784</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>46139</v>
       </c>
@@ -3249,7 +3310,7 @@
         <v>15</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>48</v>
@@ -3258,7 +3319,7 @@
         <v>8952.2999999999993</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>46139</v>
       </c>
@@ -3269,7 +3330,7 @@
         <v>15</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>32</v>
+        <v>230</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>69</v>
@@ -3278,7 +3339,7 @@
         <v>3795.01</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>46139</v>
       </c>
@@ -3289,7 +3350,7 @@
         <v>15</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>35</v>
+        <v>237</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>70</v>
@@ -3298,7 +3359,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>46139</v>
       </c>
@@ -3309,7 +3370,7 @@
         <v>15</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>32</v>
+        <v>236</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>63</v>
@@ -3318,7 +3379,7 @@
         <v>3970.21</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>46139</v>
       </c>
@@ -3329,7 +3390,7 @@
         <v>15</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>32</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>9</v>
@@ -3338,7 +3399,7 @@
         <v>15370</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>46139</v>
       </c>
@@ -3349,7 +3410,7 @@
         <v>15</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>71</v>
@@ -3358,7 +3419,7 @@
         <v>9135</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>46139</v>
       </c>
@@ -3369,7 +3430,7 @@
         <v>15</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>71</v>
@@ -3378,7 +3439,7 @@
         <v>11629</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>46139</v>
       </c>
@@ -3389,7 +3450,7 @@
         <v>15</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>71</v>
@@ -3398,7 +3459,7 @@
         <v>9135</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>46139</v>
       </c>
@@ -3409,7 +3470,7 @@
         <v>15</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>52</v>
@@ -3418,7 +3479,7 @@
         <v>19600</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>46139</v>
       </c>
@@ -3429,7 +3490,7 @@
         <v>15</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>72</v>
@@ -3438,7 +3499,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>46139</v>
       </c>
@@ -3449,7 +3510,7 @@
         <v>15</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>73</v>
@@ -3458,7 +3519,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>46139</v>
       </c>
@@ -3469,7 +3530,7 @@
         <v>15</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>32</v>
+        <v>236</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>74</v>
@@ -3478,7 +3539,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>46139</v>
       </c>
@@ -3498,7 +3559,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>46139</v>
       </c>
@@ -3509,7 +3570,7 @@
         <v>15</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>76</v>
@@ -3518,7 +3579,7 @@
         <v>3310</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>46139</v>
       </c>
@@ -3529,7 +3590,7 @@
         <v>15</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>77</v>
@@ -3538,7 +3599,7 @@
         <v>12220</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>46139</v>
       </c>
@@ -3558,7 +3619,7 @@
         <v>2516.21</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>46139</v>
       </c>
@@ -3578,7 +3639,7 @@
         <v>11600</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>46139</v>
       </c>
@@ -3589,7 +3650,7 @@
         <v>15</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>32</v>
+        <v>224</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>80</v>
@@ -3598,7 +3659,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>46139</v>
       </c>
@@ -3609,7 +3670,7 @@
         <v>15</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>28</v>
@@ -3618,7 +3679,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>46139</v>
       </c>
@@ -3629,7 +3690,7 @@
         <v>15</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>21</v>
@@ -3638,7 +3699,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>46139</v>
       </c>
@@ -3649,7 +3710,7 @@
         <v>15</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>22</v>
@@ -3658,7 +3719,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>46139</v>
       </c>
@@ -3669,7 +3730,7 @@
         <v>15</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>81</v>
@@ -3678,7 +3739,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>46139</v>
       </c>
@@ -3689,7 +3750,7 @@
         <v>15</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>24</v>
@@ -3698,7 +3759,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>46139</v>
       </c>
@@ -3709,7 +3770,7 @@
         <v>15</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>27</v>
@@ -3718,7 +3779,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>46139</v>
       </c>
@@ -3729,7 +3790,7 @@
         <v>15</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>57</v>
@@ -3738,7 +3799,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>46139</v>
       </c>
@@ -3758,7 +3819,7 @@
         <v>121000</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>46139</v>
       </c>
@@ -3778,7 +3839,7 @@
         <v>212976</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>46132</v>
       </c>
@@ -3798,7 +3859,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>46132</v>
       </c>
@@ -3818,7 +3879,7 @@
         <v>31050</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>46132</v>
       </c>
@@ -3829,7 +3890,7 @@
         <v>15</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>47</v>
@@ -3838,7 +3899,7 @@
         <v>40426.65</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>46132</v>
       </c>
@@ -3849,7 +3910,7 @@
         <v>15</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>85</v>
@@ -3858,7 +3919,7 @@
         <v>13310.119999999999</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
         <v>46132</v>
       </c>
@@ -3869,7 +3930,7 @@
         <v>15</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>32</v>
+        <v>224</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>86</v>
@@ -3878,7 +3939,7 @@
         <v>1441.56</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>46132</v>
       </c>
@@ -3898,7 +3959,7 @@
         <v>13727.7</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>46132</v>
       </c>
@@ -3909,7 +3970,7 @@
         <v>15</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>87</v>
@@ -3918,7 +3979,7 @@
         <v>31642.400000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>46132</v>
       </c>
@@ -3938,7 +3999,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>46132</v>
       </c>
@@ -3949,7 +4010,7 @@
         <v>15</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>88</v>
@@ -3958,7 +4019,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>46132</v>
       </c>
@@ -3969,7 +4030,7 @@
         <v>15</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>71</v>
@@ -3978,7 +4039,7 @@
         <v>28739</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>46132</v>
       </c>
@@ -3989,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>71</v>
@@ -3998,7 +4059,7 @@
         <v>9801.9999999999982</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>46132</v>
       </c>
@@ -4009,7 +4070,7 @@
         <v>15</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>32</v>
+        <v>230</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>12</v>
@@ -4018,7 +4079,7 @@
         <v>2277.13</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>46132</v>
       </c>
@@ -4029,7 +4090,7 @@
         <v>15</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>32</v>
+        <v>224</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>89</v>
@@ -4038,7 +4099,7 @@
         <v>3888</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>46132</v>
       </c>
@@ -4049,7 +4110,7 @@
         <v>15</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>90</v>
@@ -4058,7 +4119,7 @@
         <v>85800</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>46132</v>
       </c>
@@ -4069,7 +4130,7 @@
         <v>15</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>90</v>
@@ -4078,7 +4139,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>46132</v>
       </c>
@@ -4089,7 +4150,7 @@
         <v>15</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>77</v>
@@ -4098,7 +4159,7 @@
         <v>12424.75</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>46132</v>
       </c>
@@ -4109,7 +4170,7 @@
         <v>15</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>117</v>
+        <v>223</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>91</v>
@@ -4118,7 +4179,7 @@
         <v>18768</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>46132</v>
       </c>
@@ -4129,7 +4190,7 @@
         <v>15</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>28</v>
@@ -4138,7 +4199,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>46132</v>
       </c>
@@ -4149,7 +4210,7 @@
         <v>15</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>21</v>
@@ -4158,7 +4219,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>46132</v>
       </c>
@@ -4169,7 +4230,7 @@
         <v>15</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>22</v>
@@ -4178,7 +4239,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>46132</v>
       </c>
@@ -4189,7 +4250,7 @@
         <v>15</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>92</v>
@@ -4198,7 +4259,7 @@
         <v>5800</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>46132</v>
       </c>
@@ -4209,7 +4270,7 @@
         <v>15</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>93</v>
@@ -4218,7 +4279,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>46132</v>
       </c>
@@ -4229,7 +4290,7 @@
         <v>15</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>81</v>
@@ -4238,7 +4299,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>46132</v>
       </c>
@@ -4249,7 +4310,7 @@
         <v>15</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>24</v>
@@ -4258,7 +4319,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>46132</v>
       </c>
@@ -4269,7 +4330,7 @@
         <v>15</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>27</v>
@@ -4278,7 +4339,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>46132</v>
       </c>
@@ -4289,7 +4350,7 @@
         <v>15</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>57</v>
@@ -4298,7 +4359,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>46132</v>
       </c>
@@ -4318,7 +4379,7 @@
         <v>121000</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>46132</v>
       </c>
@@ -4338,7 +4399,7 @@
         <v>126412</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
         <v>46132</v>
       </c>
@@ -4358,7 +4419,7 @@
         <v>126396.8</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>46132</v>
       </c>
@@ -4378,7 +4439,7 @@
         <v>151064.4</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>46125</v>
       </c>
@@ -4398,7 +4459,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>46125</v>
       </c>
@@ -4418,7 +4479,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>46125</v>
       </c>
@@ -4438,7 +4499,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>46125</v>
       </c>
@@ -4458,7 +4519,7 @@
         <v>5250</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>46125</v>
       </c>
@@ -4469,7 +4530,7 @@
         <v>15</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>87</v>
@@ -4478,7 +4539,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>46125</v>
       </c>
@@ -4498,7 +4559,7 @@
         <v>9676.4500000000007</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>46125</v>
       </c>
@@ -4518,7 +4579,7 @@
         <v>12652.68</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>46125</v>
       </c>
@@ -4529,7 +4590,7 @@
         <v>15</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>71</v>
@@ -4538,7 +4599,7 @@
         <v>18270</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>46125</v>
       </c>
@@ -4549,7 +4610,7 @@
         <v>15</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>28</v>
@@ -4558,7 +4619,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>46125</v>
       </c>
@@ -4569,7 +4630,7 @@
         <v>15</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>21</v>
@@ -4578,7 +4639,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>46125</v>
       </c>
@@ -4589,7 +4650,7 @@
         <v>15</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>22</v>
@@ -4598,7 +4659,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>46125</v>
       </c>
@@ -4609,7 +4670,7 @@
         <v>15</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>92</v>
@@ -4618,7 +4679,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>46125</v>
       </c>
@@ -4629,7 +4690,7 @@
         <v>15</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>24</v>
@@ -4638,7 +4699,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>46125</v>
       </c>
@@ -4649,7 +4710,7 @@
         <v>15</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>27</v>
@@ -4658,7 +4719,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>46125</v>
       </c>
@@ -4669,7 +4730,7 @@
         <v>15</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>97</v>
@@ -4678,7 +4739,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>46125</v>
       </c>
@@ -4698,7 +4759,7 @@
         <v>126412</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>46125</v>
       </c>
@@ -4718,7 +4779,7 @@
         <v>67394.080000000016</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>46125</v>
       </c>
@@ -4738,7 +4799,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>46118</v>
       </c>
@@ -4758,7 +4819,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
         <v>46118</v>
       </c>
@@ -4778,7 +4839,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>46118</v>
       </c>
@@ -4798,7 +4859,7 @@
         <v>21950</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="4">
         <v>46118</v>
       </c>
@@ -4809,7 +4870,7 @@
         <v>15</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>68</v>
@@ -4818,7 +4879,7 @@
         <v>2784</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>46118</v>
       </c>
@@ -4829,7 +4890,7 @@
         <v>15</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>32</v>
+        <v>230</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>69</v>
@@ -4838,7 +4899,7 @@
         <v>3795.02</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="4">
         <v>46118</v>
       </c>
@@ -4858,7 +4919,7 @@
         <v>4701.9000000000005</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>46118</v>
       </c>
@@ -4869,7 +4930,7 @@
         <v>15</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>71</v>
@@ -4878,7 +4939,7 @@
         <v>9135</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>46118</v>
       </c>
@@ -4889,7 +4950,7 @@
         <v>15</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>28</v>
@@ -4898,7 +4959,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>46118</v>
       </c>
@@ -4909,7 +4970,7 @@
         <v>15</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>21</v>
@@ -4918,7 +4979,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
         <v>46118</v>
       </c>
@@ -4929,7 +4990,7 @@
         <v>15</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>22</v>
@@ -4938,7 +4999,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>46118</v>
       </c>
@@ -4949,7 +5010,7 @@
         <v>15</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>92</v>
@@ -4958,7 +5019,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
         <v>46118</v>
       </c>
@@ -4969,7 +5030,7 @@
         <v>15</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>24</v>
@@ -4978,7 +5039,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>46118</v>
       </c>
@@ -4989,7 +5050,7 @@
         <v>15</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>27</v>
@@ -4998,7 +5059,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>46118</v>
       </c>
@@ -5018,7 +5079,7 @@
         <v>199760</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>46111</v>
       </c>
@@ -5038,7 +5099,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>46111</v>
       </c>
@@ -5058,7 +5119,7 @@
         <v>17950</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>46111</v>
       </c>
@@ -5078,7 +5139,7 @@
         <v>5163.9000000000005</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>46111</v>
       </c>
@@ -5089,7 +5150,7 @@
         <v>15</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>105</v>
@@ -5098,7 +5159,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>46111</v>
       </c>
@@ -5109,7 +5170,7 @@
         <v>15</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>28</v>
@@ -5118,7 +5179,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="4">
         <v>46111</v>
       </c>
@@ -5129,7 +5190,7 @@
         <v>15</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>21</v>
@@ -5138,7 +5199,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>46111</v>
       </c>
@@ -5149,7 +5210,7 @@
         <v>15</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>22</v>
@@ -5158,7 +5219,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>46111</v>
       </c>
@@ -5169,7 +5230,7 @@
         <v>15</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>35</v>
+        <v>233</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>106</v>
@@ -5178,7 +5239,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>46111</v>
       </c>
@@ -5189,7 +5250,7 @@
         <v>15</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>24</v>
@@ -5198,7 +5259,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="4">
         <v>46111</v>
       </c>
@@ -5209,7 +5270,7 @@
         <v>15</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>27</v>
@@ -5218,7 +5279,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>46111</v>
       </c>
@@ -5238,7 +5299,7 @@
         <v>99880</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
         <v>46111</v>
       </c>
@@ -5258,7 +5319,7 @@
         <v>33000</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>46104</v>
       </c>
@@ -5278,7 +5339,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="4">
         <v>46104</v>
       </c>
@@ -5298,7 +5359,7 @@
         <v>10800</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
         <v>46104</v>
       </c>
@@ -5318,7 +5379,7 @@
         <v>16950</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
         <v>46104</v>
       </c>
@@ -5338,7 +5399,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="4">
         <v>46104</v>
       </c>
@@ -5349,7 +5410,7 @@
         <v>15</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>32</v>
+        <v>224</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>108</v>
@@ -5358,7 +5419,7 @@
         <v>2501.41</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="4">
         <v>46104</v>
       </c>
@@ -5378,7 +5439,7 @@
         <v>5365.5</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>46104</v>
       </c>
@@ -5389,7 +5450,7 @@
         <v>15</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>35</v>
+        <v>231</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>109</v>
@@ -5398,7 +5459,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
         <v>46104</v>
       </c>
@@ -5418,7 +5479,7 @@
         <v>7540</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
         <v>46104</v>
       </c>
@@ -5429,7 +5490,7 @@
         <v>15</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>28</v>
@@ -5438,7 +5499,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>46104</v>
       </c>
@@ -5449,7 +5510,7 @@
         <v>15</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>21</v>
@@ -5458,7 +5519,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>46104</v>
       </c>
@@ -5469,7 +5530,7 @@
         <v>15</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>22</v>
@@ -5478,7 +5539,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="4">
         <v>46104</v>
       </c>
@@ -5489,7 +5550,7 @@
         <v>15</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>35</v>
+        <v>233</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>106</v>
@@ -5498,7 +5559,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="4">
         <v>46104</v>
       </c>
@@ -5509,7 +5570,7 @@
         <v>15</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>24</v>
@@ -5518,7 +5579,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
         <v>46104</v>
       </c>
@@ -5529,7 +5590,7 @@
         <v>15</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>27</v>
@@ -5538,7 +5599,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>46104</v>
       </c>
@@ -5558,7 +5619,7 @@
         <v>203456</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
         <v>46097</v>
       </c>
@@ -5578,7 +5639,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
         <v>46097</v>
       </c>
@@ -5598,7 +5659,7 @@
         <v>10800</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="4">
         <v>46097</v>
       </c>
@@ -5618,7 +5679,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
         <v>46097</v>
       </c>
@@ -5629,7 +5690,7 @@
         <v>15</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>68</v>
@@ -5638,7 +5699,7 @@
         <v>3828</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
         <v>46097</v>
       </c>
@@ -5658,7 +5719,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>46097</v>
       </c>
@@ -5678,7 +5739,7 @@
         <v>6323.1</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
         <v>46097</v>
       </c>
@@ -5689,7 +5750,7 @@
         <v>15</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>32</v>
+        <v>236</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>63</v>
@@ -5698,7 +5759,7 @@
         <v>3410</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="4">
         <v>46097</v>
       </c>
@@ -5718,7 +5779,7 @@
         <v>7499</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
         <v>46097</v>
       </c>
@@ -5729,7 +5790,7 @@
         <v>15</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>28</v>
@@ -5738,7 +5799,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="4">
         <v>46097</v>
       </c>
@@ -5749,7 +5810,7 @@
         <v>15</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>21</v>
@@ -5758,7 +5819,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="4">
         <v>46097</v>
       </c>
@@ -5769,7 +5830,7 @@
         <v>15</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>22</v>
@@ -5778,7 +5839,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
         <v>46097</v>
       </c>
@@ -5789,7 +5850,7 @@
         <v>15</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>35</v>
+        <v>233</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>106</v>
@@ -5798,7 +5859,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="4">
         <v>46097</v>
       </c>
@@ -5809,7 +5870,7 @@
         <v>15</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>24</v>
@@ -5818,7 +5879,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
         <v>46097</v>
       </c>
@@ -5829,7 +5890,7 @@
         <v>15</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>27</v>
@@ -5838,7 +5899,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
         <v>46097</v>
       </c>
@@ -5858,7 +5919,7 @@
         <v>199760</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>46097</v>
       </c>
@@ -5878,7 +5939,7 @@
         <v>129030</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
         <v>46090</v>
       </c>
@@ -5898,7 +5959,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
         <v>46090</v>
       </c>
@@ -5918,7 +5979,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="4">
         <v>46090</v>
       </c>
@@ -5929,7 +5990,7 @@
         <v>15</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>47</v>
@@ -5938,7 +5999,7 @@
         <v>24415.439999999999</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>46090</v>
       </c>
@@ -5949,7 +6010,7 @@
         <v>15</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>85</v>
@@ -5958,7 +6019,7 @@
         <v>1493.5</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
         <v>46090</v>
       </c>
@@ -5978,7 +6039,7 @@
         <v>6822.9840000000004</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>46090</v>
       </c>
@@ -5989,7 +6050,7 @@
         <v>15</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>105</v>
@@ -5998,7 +6059,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>46090</v>
       </c>
@@ -6009,7 +6070,7 @@
         <v>15</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>52</v>
@@ -6018,7 +6079,7 @@
         <v>10452</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
         <v>46090</v>
       </c>
@@ -6038,7 +6099,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
         <v>46090</v>
       </c>
@@ -6049,7 +6110,7 @@
         <v>15</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>28</v>
@@ -6058,7 +6119,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>46090</v>
       </c>
@@ -6069,7 +6130,7 @@
         <v>15</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>21</v>
@@ -6078,7 +6139,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="4">
         <v>46090</v>
       </c>
@@ -6089,7 +6150,7 @@
         <v>15</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>22</v>
@@ -6098,7 +6159,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
         <v>46090</v>
       </c>
@@ -6109,7 +6170,7 @@
         <v>15</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>35</v>
+        <v>233</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>106</v>
@@ -6118,7 +6179,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>46090</v>
       </c>
@@ -6129,7 +6190,7 @@
         <v>15</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>24</v>
@@ -6138,7 +6199,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
         <v>46090</v>
       </c>
@@ -6149,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>116</v>
@@ -6158,7 +6219,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="4">
         <v>46090</v>
       </c>
@@ -6169,7 +6230,7 @@
         <v>15</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>27</v>
@@ -6178,7 +6239,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>46090</v>
       </c>
@@ -6198,7 +6259,7 @@
         <v>199760</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
         <v>46090</v>
       </c>
@@ -6218,7 +6279,7 @@
         <v>129030</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
         <v>46083</v>
       </c>
@@ -6238,7 +6299,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
         <v>46083</v>
       </c>
@@ -6258,7 +6319,7 @@
         <v>19950</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="4">
         <v>46083</v>
       </c>
@@ -6269,7 +6330,7 @@
         <v>15</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>47</v>
@@ -6278,7 +6339,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="4">
         <v>46083</v>
       </c>
@@ -6289,7 +6350,7 @@
         <v>15</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>19</v>
+        <v>225</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>119</v>
@@ -6298,7 +6359,7 @@
         <v>6811.7</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
         <v>46083</v>
       </c>
@@ -6318,7 +6379,7 @@
         <v>5457.9000000000005</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="4">
         <v>46083</v>
       </c>
@@ -6329,7 +6390,7 @@
         <v>15</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>120</v>
@@ -6338,7 +6399,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
         <v>46083</v>
       </c>
@@ -6349,7 +6410,7 @@
         <v>15</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>71</v>
@@ -6358,7 +6419,7 @@
         <v>1896.6</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
         <v>46083</v>
       </c>
@@ -6378,7 +6439,7 @@
         <v>8120</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
         <v>46083</v>
       </c>
@@ -6389,7 +6450,7 @@
         <v>15</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>52</v>
@@ -6398,7 +6459,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
         <v>46083</v>
       </c>
@@ -6409,7 +6470,7 @@
         <v>15</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>32</v>
+        <v>227</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>122</v>
@@ -6418,7 +6479,7 @@
         <v>2868</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>46083</v>
       </c>
@@ -6429,7 +6490,7 @@
         <v>15</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>28</v>
@@ -6438,7 +6499,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
         <v>46083</v>
       </c>
@@ -6449,7 +6510,7 @@
         <v>15</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>123</v>
@@ -6458,7 +6519,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
         <v>46083</v>
       </c>
@@ -6469,7 +6530,7 @@
         <v>15</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>21</v>
@@ -6478,7 +6539,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>46083</v>
       </c>
@@ -6489,7 +6550,7 @@
         <v>15</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>22</v>
@@ -6498,7 +6559,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>46083</v>
       </c>
@@ -6509,7 +6570,7 @@
         <v>15</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>24</v>
@@ -6518,7 +6579,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>46083</v>
       </c>
@@ -6529,7 +6590,7 @@
         <v>15</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>116</v>
@@ -6538,7 +6599,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>46083</v>
       </c>
@@ -6549,7 +6610,7 @@
         <v>15</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>27</v>
@@ -6558,7 +6619,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
         <v>46083</v>
       </c>
@@ -6578,7 +6639,7 @@
         <v>199760</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
         <v>46083</v>
       </c>
@@ -6598,7 +6659,7 @@
         <v>129030</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
         <v>46076</v>
       </c>
@@ -6618,7 +6679,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="4">
         <v>46076</v>
       </c>
@@ -6638,7 +6699,7 @@
         <v>21800</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
         <v>46076</v>
       </c>
@@ -6649,7 +6710,7 @@
         <v>15</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>47</v>
@@ -6658,7 +6719,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="4">
         <v>46076</v>
       </c>
@@ -6669,7 +6730,7 @@
         <v>15</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>4</v>
@@ -6678,7 +6739,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="4">
         <v>46076</v>
       </c>
@@ -6689,7 +6750,7 @@
         <v>15</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>19</v>
+        <v>225</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>119</v>
@@ -6698,7 +6759,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="4">
         <v>46076</v>
       </c>
@@ -6718,7 +6779,7 @@
         <v>5115.6000000000004</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="4">
         <v>46076</v>
       </c>
@@ -6729,7 +6790,7 @@
         <v>15</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>88</v>
@@ -6738,7 +6799,7 @@
         <v>7250</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
         <v>46076</v>
       </c>
@@ -6749,7 +6810,7 @@
         <v>15</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>71</v>
@@ -6758,7 +6819,7 @@
         <v>9801.9999999999982</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="4">
         <v>46076</v>
       </c>
@@ -6769,7 +6830,7 @@
         <v>15</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>52</v>
@@ -6778,7 +6839,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="4">
         <v>46076</v>
       </c>
@@ -6789,7 +6850,7 @@
         <v>15</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>27</v>
@@ -6798,7 +6859,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="4">
         <v>46076</v>
       </c>
@@ -6809,7 +6870,7 @@
         <v>15</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>28</v>
@@ -6818,7 +6879,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="4">
         <v>46076</v>
       </c>
@@ -6829,7 +6890,7 @@
         <v>15</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>123</v>
@@ -6838,7 +6899,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="4">
         <v>46076</v>
       </c>
@@ -6849,7 +6910,7 @@
         <v>15</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>21</v>
@@ -6858,7 +6919,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="4">
         <v>46076</v>
       </c>
@@ -6869,7 +6930,7 @@
         <v>15</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>22</v>
@@ -6878,7 +6939,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="4">
         <v>46076</v>
       </c>
@@ -6889,7 +6950,7 @@
         <v>15</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>24</v>
@@ -6898,7 +6959,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="4">
         <v>46076</v>
       </c>
@@ -6909,7 +6970,7 @@
         <v>15</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>116</v>
@@ -6918,7 +6979,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="4">
         <v>46076</v>
       </c>
@@ -6929,7 +6990,7 @@
         <v>15</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>27</v>
@@ -6938,7 +6999,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="4">
         <v>46076</v>
       </c>
@@ -6958,7 +7019,7 @@
         <v>39100</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="4">
         <v>46076</v>
       </c>
@@ -6978,7 +7039,7 @@
         <v>188000</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="4">
         <v>46069</v>
       </c>
@@ -6998,7 +7059,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="4">
         <v>46069</v>
       </c>
@@ -7018,7 +7079,7 @@
         <v>15950</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="4">
         <v>46069</v>
       </c>
@@ -7029,7 +7090,7 @@
         <v>15</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>127</v>
@@ -7038,7 +7099,7 @@
         <v>5916</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="4">
         <v>46069</v>
       </c>
@@ -7049,7 +7110,7 @@
         <v>15</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>4</v>
@@ -7058,7 +7119,7 @@
         <v>19999.8</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="4">
         <v>46069</v>
       </c>
@@ -7069,7 +7130,7 @@
         <v>15</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>19</v>
+        <v>225</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>119</v>
@@ -7078,7 +7139,7 @@
         <v>4045.02</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="4">
         <v>46069</v>
       </c>
@@ -7089,7 +7150,7 @@
         <v>15</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>128</v>
@@ -7098,7 +7159,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="4">
         <v>46069</v>
       </c>
@@ -7118,7 +7179,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="4">
         <v>46069</v>
       </c>
@@ -7129,7 +7190,7 @@
         <v>15</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>88</v>
@@ -7138,7 +7199,7 @@
         <v>7250</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="4">
         <v>46069</v>
       </c>
@@ -7149,7 +7210,7 @@
         <v>15</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>71</v>
@@ -7158,7 +7219,7 @@
         <v>9801.9999999999982</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="4">
         <v>46069</v>
       </c>
@@ -7178,7 +7239,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="4">
         <v>46069</v>
       </c>
@@ -7189,7 +7250,7 @@
         <v>15</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>28</v>
@@ -7198,7 +7259,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="4">
         <v>46069</v>
       </c>
@@ -7209,7 +7270,7 @@
         <v>15</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>123</v>
@@ -7218,7 +7279,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="4">
         <v>46069</v>
       </c>
@@ -7229,7 +7290,7 @@
         <v>15</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>21</v>
@@ -7238,7 +7299,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="4">
         <v>46069</v>
       </c>
@@ -7249,7 +7310,7 @@
         <v>15</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>22</v>
@@ -7258,7 +7319,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="4">
         <v>46069</v>
       </c>
@@ -7269,7 +7330,7 @@
         <v>15</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>24</v>
@@ -7278,7 +7339,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="4">
         <v>46069</v>
       </c>
@@ -7289,7 +7350,7 @@
         <v>15</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>27</v>
@@ -7298,7 +7359,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" s="4">
         <v>46069</v>
       </c>
@@ -7318,7 +7379,7 @@
         <v>198200</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" s="4">
         <v>46069</v>
       </c>
@@ -7338,7 +7399,7 @@
         <v>39100</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" s="4">
         <v>46069</v>
       </c>
@@ -7358,7 +7419,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" s="4">
         <v>46062</v>
       </c>
@@ -7378,7 +7439,7 @@
         <v>98000</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" s="4">
         <v>46062</v>
       </c>
@@ -7398,7 +7459,7 @@
         <v>9950</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" s="4">
         <v>46062</v>
       </c>
@@ -7409,7 +7470,7 @@
         <v>15</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>47</v>
@@ -7418,7 +7479,7 @@
         <v>27783.47</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" s="4">
         <v>46062</v>
       </c>
@@ -7429,7 +7490,7 @@
         <v>15</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>127</v>
@@ -7438,7 +7499,7 @@
         <v>3940.45</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" s="4">
         <v>46062</v>
       </c>
@@ -7458,7 +7519,7 @@
         <v>3920</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" s="4">
         <v>46062</v>
       </c>
@@ -7478,7 +7539,7 @@
         <v>28500</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" s="4">
         <v>46062</v>
       </c>
@@ -7489,7 +7550,7 @@
         <v>15</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>32</v>
+        <v>236</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>63</v>
@@ -7498,7 +7559,7 @@
         <v>2728.32</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
         <v>46062</v>
       </c>
@@ -7509,7 +7570,7 @@
         <v>15</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>120</v>
@@ -7518,7 +7579,7 @@
         <v>33328.910000000003</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" s="4">
         <v>46062</v>
       </c>
@@ -7538,7 +7599,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" s="4">
         <v>46062</v>
       </c>
@@ -7549,7 +7610,7 @@
         <v>15</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>21</v>
@@ -7558,7 +7619,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" s="4">
         <v>46062</v>
       </c>
@@ -7569,7 +7630,7 @@
         <v>15</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>22</v>
@@ -7578,7 +7639,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" s="4">
         <v>46062</v>
       </c>
@@ -7589,7 +7650,7 @@
         <v>15</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>24</v>
@@ -7598,7 +7659,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="4">
         <v>46062</v>
       </c>
@@ -7618,7 +7679,7 @@
         <v>190680</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" s="4">
         <v>46062</v>
       </c>
@@ -7638,7 +7699,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" s="4">
         <v>46062</v>
       </c>
@@ -7649,7 +7710,7 @@
         <v>31</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>34</v>
+        <v>238</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>136</v>
@@ -7658,7 +7719,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" s="4">
         <v>46054</v>
       </c>
@@ -7678,7 +7739,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" s="4">
         <v>46054</v>
       </c>
@@ -7698,7 +7759,7 @@
         <v>19950</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" s="4">
         <v>46054</v>
       </c>
@@ -7709,7 +7770,7 @@
         <v>15</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>47</v>
@@ -7718,7 +7779,7 @@
         <v>29000</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" s="4">
         <v>46054</v>
       </c>
@@ -7729,7 +7790,7 @@
         <v>15</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>4</v>
@@ -7738,7 +7799,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" s="4">
         <v>46054</v>
       </c>
@@ -7758,7 +7819,7 @@
         <v>5608</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" s="4">
         <v>46054</v>
       </c>
@@ -7769,7 +7830,7 @@
         <v>15</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>120</v>
@@ -7778,7 +7839,7 @@
         <v>44000</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" s="4">
         <v>46054</v>
       </c>
@@ -7789,7 +7850,7 @@
         <v>15</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>28</v>
@@ -7798,7 +7859,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" s="4">
         <v>46054</v>
       </c>
@@ -7809,7 +7870,7 @@
         <v>15</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>123</v>
@@ -7818,7 +7879,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" s="4">
         <v>46054</v>
       </c>
@@ -7829,7 +7890,7 @@
         <v>15</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>21</v>
@@ -7838,7 +7899,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" s="4">
         <v>46054</v>
       </c>
@@ -7849,7 +7910,7 @@
         <v>15</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>22</v>
@@ -7858,7 +7919,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" s="4">
         <v>46054</v>
       </c>
@@ -7869,7 +7930,7 @@
         <v>15</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>24</v>
@@ -7878,7 +7939,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" s="4">
         <v>46054</v>
       </c>
@@ -7889,7 +7950,7 @@
         <v>15</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>27</v>
@@ -7898,7 +7959,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335" s="4">
         <v>46054</v>
       </c>
@@ -7918,7 +7979,7 @@
         <v>40800</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336" s="4">
         <v>46054</v>
       </c>
@@ -7938,7 +7999,7 @@
         <v>5168</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" s="4">
         <v>46054</v>
       </c>
@@ -7958,7 +8019,7 @@
         <v>203456</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" s="4">
         <v>46048</v>
       </c>
@@ -7978,7 +8039,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" s="4">
         <v>46048</v>
       </c>
@@ -7998,7 +8059,7 @@
         <v>14950</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" s="4">
         <v>46048</v>
       </c>
@@ -8009,7 +8070,7 @@
         <v>15</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>4</v>
@@ -8018,7 +8079,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" s="4">
         <v>46048</v>
       </c>
@@ -8038,7 +8099,7 @@
         <v>13226</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" s="4">
         <v>46048</v>
       </c>
@@ -8058,7 +8119,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343" s="4">
         <v>46048</v>
       </c>
@@ -8069,7 +8130,7 @@
         <v>15</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>71</v>
@@ -8078,7 +8139,7 @@
         <v>9801.9999999999982</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" s="4">
         <v>46048</v>
       </c>
@@ -8089,7 +8150,7 @@
         <v>15</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>21</v>
@@ -8098,7 +8159,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" s="4">
         <v>46048</v>
       </c>
@@ -8109,7 +8170,7 @@
         <v>15</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>22</v>
@@ -8118,7 +8179,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" s="4">
         <v>46048</v>
       </c>
@@ -8129,7 +8190,7 @@
         <v>15</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>35</v>
+        <v>233</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>106</v>
@@ -8138,7 +8199,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" s="4">
         <v>46048</v>
       </c>
@@ -8149,7 +8210,7 @@
         <v>15</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>24</v>
@@ -8158,7 +8219,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" s="4">
         <v>46048</v>
       </c>
@@ -8169,7 +8230,7 @@
         <v>15</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>27</v>
@@ -8178,7 +8239,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" s="4">
         <v>46048</v>
       </c>
@@ -8198,7 +8259,7 @@
         <v>117920</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" s="4">
         <v>46048</v>
       </c>
@@ -8218,7 +8279,7 @@
         <v>203456</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" s="4">
         <v>46041</v>
       </c>
@@ -8238,7 +8299,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" s="4">
         <v>46041</v>
       </c>
@@ -8258,7 +8319,7 @@
         <v>25250</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A353" s="4">
         <v>46041</v>
       </c>
@@ -8278,7 +8339,7 @@
         <v>6632.96</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A354" s="4">
         <v>46041</v>
       </c>
@@ -8289,7 +8350,7 @@
         <v>15</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>145</v>
@@ -8298,7 +8359,7 @@
         <v>3897.6</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A355" s="4">
         <v>46041</v>
       </c>
@@ -8309,7 +8370,7 @@
         <v>15</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>146</v>
@@ -8318,7 +8379,7 @@
         <v>16800</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A356" s="4">
         <v>46041</v>
       </c>
@@ -8329,7 +8390,7 @@
         <v>15</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>28</v>
@@ -8338,7 +8399,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A357" s="4">
         <v>46041</v>
       </c>
@@ -8349,7 +8410,7 @@
         <v>15</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>123</v>
@@ -8358,7 +8419,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A358" s="4">
         <v>46041</v>
       </c>
@@ -8369,7 +8430,7 @@
         <v>15</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>21</v>
@@ -8378,7 +8439,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A359" s="4">
         <v>46041</v>
       </c>
@@ -8389,7 +8450,7 @@
         <v>15</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>147</v>
@@ -8398,7 +8459,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A360" s="4">
         <v>46041</v>
       </c>
@@ -8409,7 +8470,7 @@
         <v>15</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>22</v>
@@ -8418,7 +8479,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A361" s="4">
         <v>46041</v>
       </c>
@@ -8429,7 +8490,7 @@
         <v>15</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>24</v>
@@ -8438,7 +8499,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A362" s="4">
         <v>46041</v>
       </c>
@@ -8449,7 +8510,7 @@
         <v>15</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>148</v>
@@ -8458,7 +8519,7 @@
         <v>1316.6666666666667</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A363" s="4">
         <v>46041</v>
       </c>
@@ -8469,7 +8530,7 @@
         <v>15</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>27</v>
@@ -8478,7 +8539,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A364" s="4">
         <v>46041</v>
       </c>
@@ -8498,7 +8559,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A365" s="4">
         <v>46041</v>
       </c>
@@ -8518,7 +8579,7 @@
         <v>65824</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A366" s="4">
         <v>46033</v>
       </c>
@@ -8538,7 +8599,7 @@
         <v>73000</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A367" s="4">
         <v>46033</v>
       </c>
@@ -8558,7 +8619,7 @@
         <v>10200</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A368" s="4">
         <v>46033</v>
       </c>
@@ -8569,7 +8630,7 @@
         <v>15</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>28</v>
@@ -8578,7 +8639,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369" s="4">
         <v>46033</v>
       </c>
@@ -8589,7 +8650,7 @@
         <v>15</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>123</v>
@@ -8598,7 +8659,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A370" s="4">
         <v>46033</v>
       </c>
@@ -8609,7 +8670,7 @@
         <v>15</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>21</v>
@@ -8618,7 +8679,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A371" s="4">
         <v>46033</v>
       </c>
@@ -8629,7 +8690,7 @@
         <v>15</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>147</v>
@@ -8638,7 +8699,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A372" s="4">
         <v>46033</v>
       </c>
@@ -8649,7 +8710,7 @@
         <v>15</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>22</v>
@@ -8658,7 +8719,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373" s="4">
         <v>46033</v>
       </c>
@@ -8669,7 +8730,7 @@
         <v>15</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>24</v>
@@ -8678,7 +8739,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374" s="4">
         <v>46033</v>
       </c>
@@ -8689,7 +8750,7 @@
         <v>15</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>148</v>
@@ -8698,7 +8759,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A375" s="4">
         <v>46033</v>
       </c>
@@ -8709,7 +8770,7 @@
         <v>15</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>27</v>
@@ -8718,7 +8779,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A376" s="4">
         <v>46033</v>
       </c>
@@ -8738,7 +8799,7 @@
         <v>47000</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A377" s="4">
         <v>46033</v>
       </c>
@@ -8758,7 +8819,7 @@
         <v>39947.519999999997</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A378" s="4">
         <v>46033</v>
       </c>
@@ -8778,7 +8839,7 @@
         <v>99317.759999999995</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A379" s="4">
         <v>46033</v>
       </c>
@@ -8798,7 +8859,7 @@
         <v>113203</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A380" s="4">
         <v>46027</v>
       </c>
@@ -8818,7 +8879,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381" s="4">
         <v>46027</v>
       </c>
@@ -8838,7 +8899,7 @@
         <v>17800</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A382" s="4">
         <v>46027</v>
       </c>
@@ -8849,7 +8910,7 @@
         <v>15</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>32</v>
+        <v>227</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>153</v>
@@ -8858,7 +8919,7 @@
         <v>3981.94</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A383" s="4">
         <v>46027</v>
       </c>
@@ -8869,7 +8930,7 @@
         <v>15</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>32</v>
+        <v>224</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>86</v>
@@ -8878,7 +8939,7 @@
         <v>2041.71</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A384" s="4">
         <v>46027</v>
       </c>
@@ -8889,7 +8950,7 @@
         <v>15</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>19</v>
+        <v>239</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>154</v>
@@ -8898,7 +8959,7 @@
         <v>15600</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A385" s="4">
         <v>46027</v>
       </c>
@@ -8909,7 +8970,7 @@
         <v>15</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>19</v>
+        <v>239</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>155</v>
@@ -8918,7 +8979,7 @@
         <v>37500</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A386" s="4">
         <v>46027</v>
       </c>
@@ -8929,7 +8990,7 @@
         <v>15</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>123</v>
@@ -8938,7 +8999,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A387" s="4">
         <v>46027</v>
       </c>
@@ -8949,7 +9010,7 @@
         <v>15</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>21</v>
@@ -8958,7 +9019,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A388" s="4">
         <v>46027</v>
       </c>
@@ -8969,7 +9030,7 @@
         <v>15</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>147</v>
@@ -8978,7 +9039,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A389" s="4">
         <v>46027</v>
       </c>
@@ -8989,7 +9050,7 @@
         <v>15</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>22</v>
@@ -8998,7 +9059,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A390" s="4">
         <v>46027</v>
       </c>
@@ -9009,7 +9070,7 @@
         <v>15</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>24</v>
@@ -9018,7 +9079,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A391" s="4">
         <v>46027</v>
       </c>
@@ -9029,7 +9090,7 @@
         <v>15</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>156</v>
@@ -9038,7 +9099,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A392" s="4">
         <v>46027</v>
       </c>
@@ -9058,7 +9119,7 @@
         <v>53100</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A393" s="4">
         <v>46027</v>
       </c>
@@ -9078,7 +9139,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A394" s="4">
         <v>46027</v>
       </c>
@@ -9098,7 +9159,7 @@
         <v>78444.800000000003</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A395" s="4">
         <v>46020</v>
       </c>
@@ -9118,7 +9179,7 @@
         <v>125037</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A396" s="4">
         <v>46020</v>
       </c>
@@ -9129,7 +9190,7 @@
         <v>15</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>4</v>
@@ -9138,7 +9199,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A397" s="4">
         <v>46020</v>
       </c>
@@ -9149,7 +9210,7 @@
         <v>15</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>159</v>
@@ -9158,7 +9219,7 @@
         <v>7308</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A398" s="4">
         <v>46020</v>
       </c>
@@ -9178,7 +9239,7 @@
         <v>9280</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A399" s="4">
         <v>46020</v>
       </c>
@@ -9198,7 +9259,7 @@
         <v>20960</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A400" s="4">
         <v>46020</v>
       </c>
@@ -9218,7 +9279,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A401" s="4">
         <v>46020</v>
       </c>
@@ -9229,7 +9290,7 @@
         <v>15</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>35</v>
+        <v>241</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>162</v>
@@ -9238,7 +9299,7 @@
         <v>6020.4</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A402" s="4">
         <v>46020</v>
       </c>
@@ -9249,7 +9310,7 @@
         <v>15</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>32</v>
+        <v>230</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>163</v>
@@ -9258,7 +9319,7 @@
         <v>3014.2</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A403" s="4">
         <v>46020</v>
       </c>
@@ -9269,7 +9330,7 @@
         <v>15</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>123</v>
@@ -9278,7 +9339,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A404" s="4">
         <v>46020</v>
       </c>
@@ -9289,7 +9350,7 @@
         <v>15</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>21</v>
@@ -9298,7 +9359,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A405" s="4">
         <v>46020</v>
       </c>
@@ -9309,7 +9370,7 @@
         <v>15</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>147</v>
@@ -9318,7 +9379,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A406" s="4">
         <v>46020</v>
       </c>
@@ -9329,7 +9390,7 @@
         <v>15</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>22</v>
@@ -9338,7 +9399,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A407" s="4">
         <v>46020</v>
       </c>
@@ -9349,7 +9410,7 @@
         <v>15</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>24</v>
@@ -9358,7 +9419,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A408" s="4">
         <v>46020</v>
       </c>
@@ -9378,7 +9439,7 @@
         <v>198000</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A409" s="4">
         <v>46012</v>
       </c>
@@ -9398,7 +9459,7 @@
         <v>104223</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A410" s="4">
         <v>46012</v>
       </c>
@@ -9418,7 +9479,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A411" s="4">
         <v>46012</v>
       </c>
@@ -9429,7 +9490,7 @@
         <v>15</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>166</v>
@@ -9438,7 +9499,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A412" s="4">
         <v>46012</v>
       </c>
@@ -9449,7 +9510,7 @@
         <v>15</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>68</v>
@@ -9458,7 +9519,7 @@
         <v>5568</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A413" s="4">
         <v>46012</v>
       </c>
@@ -9478,7 +9539,7 @@
         <v>20852.5</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A414" s="4">
         <v>46012</v>
       </c>
@@ -9489,7 +9550,7 @@
         <v>15</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>19</v>
+        <v>225</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>119</v>
@@ -9498,7 +9559,7 @@
         <v>22846.25</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A415" s="4">
         <v>46012</v>
       </c>
@@ -9509,7 +9570,7 @@
         <v>15</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>32</v>
+        <v>229</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>167</v>
@@ -9518,7 +9579,7 @@
         <v>8120</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A416" s="4">
         <v>46012</v>
       </c>
@@ -9529,7 +9590,7 @@
         <v>15</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>133</v>
@@ -9538,7 +9599,7 @@
         <v>28500</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A417" s="4">
         <v>46012</v>
       </c>
@@ -9549,7 +9610,7 @@
         <v>15</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>35</v>
+        <v>231</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>168</v>
@@ -9558,7 +9619,7 @@
         <v>260435</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A418" s="4">
         <v>46012</v>
       </c>
@@ -9578,7 +9639,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A419" s="4">
         <v>46012</v>
       </c>
@@ -9598,7 +9659,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A420" s="4">
         <v>46012</v>
       </c>
@@ -9609,7 +9670,7 @@
         <v>15</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>19</v>
+        <v>235</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>171</v>
@@ -9618,7 +9679,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A421" s="4">
         <v>46012</v>
       </c>
@@ -9629,7 +9690,7 @@
         <v>15</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>123</v>
@@ -9638,7 +9699,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A422" s="4">
         <v>46012</v>
       </c>
@@ -9649,7 +9710,7 @@
         <v>15</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>21</v>
@@ -9658,7 +9719,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A423" s="4">
         <v>46012</v>
       </c>
@@ -9669,7 +9730,7 @@
         <v>15</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>147</v>
@@ -9678,7 +9739,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A424" s="4">
         <v>46012</v>
       </c>
@@ -9689,7 +9750,7 @@
         <v>15</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>22</v>
@@ -9698,7 +9759,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A425" s="4">
         <v>46012</v>
       </c>
@@ -9709,7 +9770,7 @@
         <v>15</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>24</v>
@@ -9718,7 +9779,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A426" s="4">
         <v>46012</v>
       </c>
@@ -9738,7 +9799,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A427" s="4">
         <v>46012</v>
       </c>
@@ -9758,7 +9819,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A428" s="4">
         <v>46012</v>
       </c>
@@ -9778,7 +9839,7 @@
         <v>194026.8</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A429" s="4">
         <v>46006</v>
       </c>
@@ -9798,7 +9859,7 @@
         <v>125038</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A430" s="4">
         <v>46006</v>
       </c>
@@ -9809,7 +9870,7 @@
         <v>15</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>166</v>
@@ -9818,7 +9879,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A431" s="4">
         <v>46006</v>
       </c>
@@ -9829,7 +9890,7 @@
         <v>15</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>4</v>
@@ -9838,7 +9899,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A432" s="4">
         <v>46006</v>
       </c>
@@ -9858,7 +9919,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A433" s="4">
         <v>46006</v>
       </c>
@@ -9869,7 +9930,7 @@
         <v>15</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>32</v>
+        <v>242</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>176</v>
@@ -9878,7 +9939,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A434" s="4">
         <v>46006</v>
       </c>
@@ -9898,7 +9959,7 @@
         <v>9588.2800000000007</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A435" s="4">
         <v>46006</v>
       </c>
@@ -9909,7 +9970,7 @@
         <v>15</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>133</v>
@@ -9918,7 +9979,7 @@
         <v>28500</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A436" s="4">
         <v>46006</v>
       </c>
@@ -9929,7 +9990,7 @@
         <v>15</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>133</v>
@@ -9938,7 +9999,7 @@
         <v>10200</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437" s="4">
         <v>46006</v>
       </c>
@@ -9949,7 +10010,7 @@
         <v>15</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>177</v>
@@ -9958,7 +10019,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A438" s="4">
         <v>46006</v>
       </c>
@@ -9969,7 +10030,7 @@
         <v>15</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>145</v>
@@ -9978,7 +10039,7 @@
         <v>39208</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A439" s="4">
         <v>46006</v>
       </c>
@@ -9989,7 +10050,7 @@
         <v>15</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>32</v>
+        <v>227</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>178</v>
@@ -9998,7 +10059,7 @@
         <v>3648.39</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A440" s="4">
         <v>46006</v>
       </c>
@@ -10009,7 +10070,7 @@
         <v>15</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>35</v>
+        <v>231</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>179</v>
@@ -10018,7 +10079,7 @@
         <v>83200</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A441" s="4">
         <v>46006</v>
       </c>
@@ -10029,7 +10090,7 @@
         <v>15</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>21</v>
@@ -10038,7 +10099,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A442" s="4">
         <v>46006</v>
       </c>
@@ -10049,7 +10110,7 @@
         <v>15</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>147</v>
@@ -10058,7 +10119,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A443" s="4">
         <v>46006</v>
       </c>
@@ -10069,7 +10130,7 @@
         <v>15</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>22</v>
@@ -10078,7 +10139,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444" s="4">
         <v>46006</v>
       </c>
@@ -10089,7 +10150,7 @@
         <v>15</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>24</v>
@@ -10098,7 +10159,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A445" s="4">
         <v>46006</v>
       </c>
@@ -10118,7 +10179,7 @@
         <v>183000</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A446" s="4">
         <v>46006</v>
       </c>
@@ -10138,7 +10199,7 @@
         <v>198000</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A447" s="4">
         <v>45999</v>
       </c>
@@ -10158,7 +10219,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A448" s="4">
         <v>45999</v>
       </c>
@@ -10169,7 +10230,7 @@
         <v>15</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>127</v>
@@ -10178,7 +10239,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A449" s="4">
         <v>45999</v>
       </c>
@@ -10189,7 +10250,7 @@
         <v>15</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>4</v>
@@ -10198,7 +10259,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A450" s="4">
         <v>45999</v>
       </c>
@@ -10218,7 +10279,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A451" s="4">
         <v>45999</v>
       </c>
@@ -10229,7 +10290,7 @@
         <v>15</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>145</v>
@@ -10238,7 +10299,7 @@
         <v>19604</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A452" s="4">
         <v>45999</v>
       </c>
@@ -10249,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>35</v>
+        <v>231</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>181</v>
@@ -10258,7 +10319,7 @@
         <v>280000</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A453" s="4">
         <v>45999</v>
       </c>
@@ -10269,7 +10330,7 @@
         <v>15</v>
       </c>
       <c r="D453" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>123</v>
@@ -10278,7 +10339,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A454" s="4">
         <v>45999</v>
       </c>
@@ -10289,7 +10350,7 @@
         <v>15</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>21</v>
@@ -10298,7 +10359,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A455" s="4">
         <v>45999</v>
       </c>
@@ -10309,7 +10370,7 @@
         <v>15</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>147</v>
@@ -10318,7 +10379,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A456" s="4">
         <v>45999</v>
       </c>
@@ -10329,7 +10390,7 @@
         <v>15</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>22</v>
@@ -10338,7 +10399,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A457" s="4">
         <v>45999</v>
       </c>
@@ -10349,7 +10410,7 @@
         <v>15</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>24</v>
@@ -10358,7 +10419,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A458" s="4">
         <v>45999</v>
       </c>
@@ -10378,7 +10439,7 @@
         <v>44750</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A459" s="4">
         <v>45999</v>
       </c>
@@ -10398,7 +10459,7 @@
         <v>199760</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A460" s="4">
         <v>45999</v>
       </c>
@@ -10418,7 +10479,7 @@
         <v>201960</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A461" s="4">
         <v>45999</v>
       </c>
@@ -10438,7 +10499,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A462" s="4">
         <v>45999</v>
       </c>
@@ -10458,7 +10519,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A463" s="4">
         <v>45999</v>
       </c>
@@ -10478,7 +10539,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A464" s="4">
         <v>45999</v>
       </c>
@@ -10498,7 +10559,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A465" s="4">
         <v>45999</v>
       </c>
@@ -10518,7 +10579,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A466" s="4">
         <v>45992</v>
       </c>
@@ -10538,7 +10599,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A467" s="4">
         <v>45992</v>
       </c>
@@ -10549,7 +10610,7 @@
         <v>15</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>166</v>
@@ -10558,7 +10619,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A468" s="4">
         <v>45992</v>
       </c>
@@ -10569,7 +10630,7 @@
         <v>15</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>4</v>
@@ -10578,7 +10639,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A469" s="4">
         <v>45992</v>
       </c>
@@ -10589,7 +10650,7 @@
         <v>15</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="E469" s="1" t="s">
         <v>68</v>
@@ -10598,7 +10659,7 @@
         <v>2784</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A470" s="4">
         <v>45992</v>
       </c>
@@ -10618,7 +10679,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A471" s="4">
         <v>45992</v>
       </c>
@@ -10629,7 +10690,7 @@
         <v>15</v>
       </c>
       <c r="D471" s="1" t="s">
-        <v>19</v>
+        <v>235</v>
       </c>
       <c r="E471" s="1" t="s">
         <v>188</v>
@@ -10638,7 +10699,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A472" s="4">
         <v>45992</v>
       </c>
@@ -10649,7 +10710,7 @@
         <v>15</v>
       </c>
       <c r="D472" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E472" s="1" t="s">
         <v>189</v>
@@ -10658,7 +10719,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A473" s="4">
         <v>45992</v>
       </c>
@@ -10669,7 +10730,7 @@
         <v>15</v>
       </c>
       <c r="D473" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E473" s="1" t="s">
         <v>21</v>
@@ -10678,7 +10739,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A474" s="4">
         <v>45992</v>
       </c>
@@ -10689,7 +10750,7 @@
         <v>15</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E474" s="1" t="s">
         <v>190</v>
@@ -10698,7 +10759,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A475" s="4">
         <v>45992</v>
       </c>
@@ -10709,7 +10770,7 @@
         <v>15</v>
       </c>
       <c r="D475" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E475" s="1" t="s">
         <v>191</v>
@@ -10718,7 +10779,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A476" s="4">
         <v>45992</v>
       </c>
@@ -10729,7 +10790,7 @@
         <v>15</v>
       </c>
       <c r="D476" s="1" t="s">
-        <v>35</v>
+        <v>233</v>
       </c>
       <c r="E476" s="1" t="s">
         <v>192</v>
@@ -10738,7 +10799,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A477" s="4">
         <v>45992</v>
       </c>
@@ -10758,7 +10819,7 @@
         <v>86000</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A478" s="4">
         <v>45992</v>
       </c>
@@ -10778,7 +10839,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A479" s="4">
         <v>45992</v>
       </c>
@@ -10798,7 +10859,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A480" s="4">
         <v>45985</v>
       </c>
@@ -10818,7 +10879,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A481" s="4">
         <v>45985</v>
       </c>
@@ -10838,7 +10899,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A482" s="4">
         <v>45985</v>
       </c>
@@ -10858,7 +10919,7 @@
         <v>17470</v>
       </c>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A483" s="4">
         <v>45985</v>
       </c>
@@ -10869,7 +10930,7 @@
         <v>15</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>21</v>
@@ -10878,7 +10939,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A484" s="4">
         <v>45985</v>
       </c>
@@ -10889,7 +10950,7 @@
         <v>15</v>
       </c>
       <c r="D484" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>147</v>
@@ -10898,7 +10959,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A485" s="4">
         <v>45985</v>
       </c>
@@ -10909,7 +10970,7 @@
         <v>15</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>22</v>
@@ -10918,7 +10979,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A486" s="4">
         <v>45985</v>
       </c>
@@ -10929,7 +10990,7 @@
         <v>15</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>24</v>
@@ -10938,7 +10999,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A487" s="4">
         <v>45985</v>
       </c>
@@ -10958,7 +11019,7 @@
         <v>86000</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A488" s="4">
         <v>45985</v>
       </c>
@@ -10978,7 +11039,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A489" s="4">
         <v>45985</v>
       </c>
@@ -10998,7 +11059,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A490" s="4">
         <v>45978</v>
       </c>
@@ -11018,7 +11079,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A491" s="4">
         <v>45978</v>
       </c>
@@ -11029,7 +11090,7 @@
         <v>15</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>47</v>
@@ -11038,7 +11099,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A492" s="4">
         <v>45978</v>
       </c>
@@ -11049,7 +11110,7 @@
         <v>15</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>166</v>
@@ -11058,7 +11119,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A493" s="4">
         <v>45978</v>
       </c>
@@ -11069,7 +11130,7 @@
         <v>15</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E493" s="1" t="s">
         <v>4</v>
@@ -11078,7 +11139,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A494" s="4">
         <v>45978</v>
       </c>
@@ -11089,7 +11150,7 @@
         <v>15</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="E494" s="1" t="s">
         <v>68</v>
@@ -11098,7 +11159,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A495" s="4">
         <v>45978</v>
       </c>
@@ -11109,7 +11170,7 @@
         <v>15</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="E495" s="1" t="s">
         <v>48</v>
@@ -11118,7 +11179,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A496" s="4">
         <v>45978</v>
       </c>
@@ -11138,7 +11199,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A497" s="4">
         <v>45978</v>
       </c>
@@ -11149,7 +11210,7 @@
         <v>15</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>19</v>
+        <v>242</v>
       </c>
       <c r="E497" s="1" t="s">
         <v>198</v>
@@ -11158,7 +11219,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A498" s="4">
         <v>45978</v>
       </c>
@@ -11169,7 +11230,7 @@
         <v>15</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>32</v>
+        <v>242</v>
       </c>
       <c r="E498" s="1" t="s">
         <v>176</v>
@@ -11178,7 +11239,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A499" s="4">
         <v>45978</v>
       </c>
@@ -11198,7 +11259,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A500" s="4">
         <v>45978</v>
       </c>
@@ -11218,7 +11279,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A501" s="4">
         <v>45978</v>
       </c>
@@ -11238,7 +11299,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A502" s="4">
         <v>45971</v>
       </c>
@@ -11258,7 +11319,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A503" s="4">
         <v>45971</v>
       </c>
@@ -11269,7 +11330,7 @@
         <v>15</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E503" s="1" t="s">
         <v>47</v>
@@ -11278,7 +11339,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A504" s="4">
         <v>45971</v>
       </c>
@@ -11298,7 +11359,7 @@
         <v>37000</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A505" s="4">
         <v>45971</v>
       </c>
@@ -11309,7 +11370,7 @@
         <v>15</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E505" s="1" t="s">
         <v>166</v>
@@ -11318,7 +11379,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A506" s="4">
         <v>45971</v>
       </c>
@@ -11329,7 +11390,7 @@
         <v>15</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E506" s="1" t="s">
         <v>4</v>
@@ -11338,7 +11399,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A507" s="4">
         <v>45971</v>
       </c>
@@ -11349,7 +11410,7 @@
         <v>15</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="E507" s="1" t="s">
         <v>68</v>
@@ -11358,7 +11419,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A508" s="4">
         <v>45971</v>
       </c>
@@ -11369,7 +11430,7 @@
         <v>15</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="E508" s="1" t="s">
         <v>48</v>
@@ -11378,7 +11439,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A509" s="4">
         <v>45971</v>
       </c>
@@ -11389,7 +11450,7 @@
         <v>15</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c r="E509" s="1" t="s">
         <v>202</v>
@@ -11398,7 +11459,7 @@
         <v>12006</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A510" s="4">
         <v>45971</v>
       </c>
@@ -11418,7 +11479,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A511" s="4">
         <v>45971</v>
       </c>
@@ -11438,7 +11499,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A512" s="4">
         <v>45971</v>
       </c>
@@ -11458,7 +11519,7 @@
         <v>175500.79999999999</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A513" s="4">
         <v>45971</v>
       </c>
@@ -11478,7 +11539,7 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A514" s="4">
         <v>45964</v>
       </c>
@@ -11498,7 +11559,7 @@
         <v>41000</v>
       </c>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A515" s="4">
         <v>45964</v>
       </c>
@@ -11518,7 +11579,7 @@
         <v>44205.22</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A516" s="4">
         <v>45964</v>
       </c>
@@ -11529,7 +11590,7 @@
         <v>15</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E516" s="1" t="s">
         <v>47</v>
@@ -11538,7 +11599,7 @@
         <v>48374.59</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A517" s="4">
         <v>45964</v>
       </c>
@@ -11558,7 +11619,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A518" s="4">
         <v>45964</v>
       </c>
@@ -11578,7 +11639,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A519" s="4">
         <v>45964</v>
       </c>
@@ -11589,7 +11650,7 @@
         <v>15</v>
       </c>
       <c r="D519" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E519" s="1" t="s">
         <v>207</v>
@@ -11598,7 +11659,7 @@
         <v>205495.79200000002</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A520" s="4">
         <v>45964</v>
       </c>
@@ -11609,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="D520" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E520" s="1" t="s">
         <v>208</v>
@@ -11618,7 +11679,7 @@
         <v>230111.28</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A521" s="4">
         <v>45964</v>
       </c>
@@ -11629,7 +11690,7 @@
         <v>15</v>
       </c>
       <c r="D521" s="1" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="E521" s="1" t="s">
         <v>209</v>
@@ -11638,7 +11699,7 @@
         <v>65529</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A522" s="4">
         <v>45964</v>
       </c>
@@ -11649,7 +11710,7 @@
         <v>15</v>
       </c>
       <c r="D522" s="1" t="s">
-        <v>32</v>
+        <v>229</v>
       </c>
       <c r="E522" s="1" t="s">
         <v>210</v>
@@ -11658,7 +11719,7 @@
         <v>16240</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A523" s="4">
         <v>45964</v>
       </c>
@@ -11669,7 +11730,7 @@
         <v>15</v>
       </c>
       <c r="D523" s="1" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>68</v>
@@ -11678,7 +11739,7 @@
         <v>2784</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A524" s="4">
         <v>45964</v>
       </c>
@@ -11689,7 +11750,7 @@
         <v>15</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E524" s="1" t="s">
         <v>211</v>
@@ -11698,7 +11759,7 @@
         <v>7700</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A525" s="4">
         <v>45964</v>
       </c>
@@ -11709,7 +11770,7 @@
         <v>15</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>32</v>
+        <v>227</v>
       </c>
       <c r="E525" s="1" t="s">
         <v>212</v>
@@ -11718,7 +11779,7 @@
         <v>2532.4499999999998</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A526" s="4">
         <v>45964</v>
       </c>
@@ -11729,7 +11790,7 @@
         <v>15</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>213</v>
@@ -11738,7 +11799,7 @@
         <v>33000</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A527" s="4">
         <v>45964</v>
       </c>
@@ -11749,7 +11810,7 @@
         <v>15</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="E527" s="1" t="s">
         <v>214</v>
@@ -11758,7 +11819,7 @@
         <v>35323</v>
       </c>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A528" s="4">
         <v>45964</v>
       </c>
@@ -11778,7 +11839,7 @@
         <v>49074.84</v>
       </c>
     </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A529" s="4">
         <v>45964</v>
       </c>
@@ -11789,7 +11850,7 @@
         <v>15</v>
       </c>
       <c r="D529" s="1" t="s">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>215</v>
@@ -11798,7 +11859,7 @@
         <v>4060</v>
       </c>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A530" s="4">
         <v>45964</v>
       </c>
@@ -11809,7 +11870,7 @@
         <v>15</v>
       </c>
       <c r="D530" s="1" t="s">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="E530" s="1" t="s">
         <v>216</v>
@@ -11818,7 +11879,7 @@
         <v>4263</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A531" s="4">
         <v>45964</v>
       </c>
@@ -11829,7 +11890,7 @@
         <v>15</v>
       </c>
       <c r="D531" s="1" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="E531" s="1" t="s">
         <v>217</v>
@@ -11838,7 +11899,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A532" s="4">
         <v>45964</v>
       </c>
@@ -11849,7 +11910,7 @@
         <v>15</v>
       </c>
       <c r="D532" s="1" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="E532" s="1" t="s">
         <v>27</v>
@@ -11858,7 +11919,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A533" s="4">
         <v>45964</v>
       </c>
@@ -11869,7 +11930,7 @@
         <v>15</v>
       </c>
       <c r="D533" s="1" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="E533" s="1" t="s">
         <v>218</v>
@@ -11878,7 +11939,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A534" s="4">
         <v>45964</v>
       </c>
@@ -11898,7 +11959,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A535" s="4">
         <v>45964</v>
       </c>
@@ -11918,7 +11979,7 @@
         <v>52000</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A536" s="4">
         <v>45964</v>
       </c>
@@ -11929,7 +11990,7 @@
         <v>15</v>
       </c>
       <c r="D536" s="1" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="E536" s="1" t="s">
         <v>221</v>
@@ -11938,7 +11999,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A537" s="4">
         <v>45964</v>
       </c>

--- a/Flujo de Efectivo/Datos flujo de efectivo.xlsx
+++ b/Flujo de Efectivo/Datos flujo de efectivo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F541"/>
+  <dimension ref="A1:F537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15472,118 +15472,6 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="538">
-      <c r="A538" s="2" t="n">
-        <v>46206</v>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>03-08 julio 2026</t>
-        </is>
-      </c>
-      <c r="C538" t="inlineStr">
-        <is>
-          <t>Egreso</t>
-        </is>
-      </c>
-      <c r="D538" t="inlineStr">
-        <is>
-          <t>Proveedores Fruta</t>
-        </is>
-      </c>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>FRESERO ALEX</t>
-        </is>
-      </c>
-      <c r="F538" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" s="2" t="n">
-        <v>46206</v>
-      </c>
-      <c r="B539" t="inlineStr">
-        <is>
-          <t>03-08 julio 2026</t>
-        </is>
-      </c>
-      <c r="C539" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>1 kg Frutos Rojos</t>
-        </is>
-      </c>
-      <c r="F539" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" s="2" t="n">
-        <v>46206</v>
-      </c>
-      <c r="B540" t="inlineStr">
-        <is>
-          <t>03-08 julio 2026</t>
-        </is>
-      </c>
-      <c r="C540" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="D540" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="E540" t="inlineStr">
-        <is>
-          <t>1 kg Frutos Rojos</t>
-        </is>
-      </c>
-      <c r="F540" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" s="2" t="n">
-        <v>46206</v>
-      </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>03-08 julio 2026</t>
-        </is>
-      </c>
-      <c r="C541" t="inlineStr">
-        <is>
-          <t>Ingreso</t>
-        </is>
-      </c>
-      <c r="D541" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="E541" t="inlineStr">
-        <is>
-          <t>48 Snack</t>
-        </is>
-      </c>
-      <c r="F541" t="n">
-        <v>700</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
